--- a/DocUtils/Contents.xlsx
+++ b/DocUtils/Contents.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ctorr\Documents\Proyectos\TaesLab\DocUtils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C475B61B-13B8-4429-B65C-7E9716CF8DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1C6E67-7E87-42F4-B236-8477E963A004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="780" windowWidth="12300" windowHeight="14700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5460" yWindow="765" windowWidth="22965" windowHeight="14700" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="471">
   <si>
     <t>Name</t>
   </si>
@@ -1092,12 +1092,6 @@
     <t>Check if the matrix is square and non-negative.</t>
   </si>
   <si>
-    <t>isNonSingularMatrix</t>
-  </si>
-  <si>
-    <t>Check if the matrix (I-A) is non-singular.</t>
-  </si>
-  <si>
     <t>isObject</t>
   </si>
   <si>
@@ -1419,32 +1413,50 @@
     <t>MG</t>
   </si>
   <si>
-    <t>Display a matrix using C-like formatting.</t>
+    <t>Display a matrix A using C-like formatting.</t>
+  </si>
+  <si>
+    <t>isProductiveMatrix</t>
+  </si>
+  <si>
+    <t>Check if a matrix represents a productive matrix.</t>
+  </si>
+  <si>
+    <t>npinv</t>
+  </si>
+  <si>
+    <t>Compute inverse of M-matrix (I - A) using Gauss-Jordan elimination.</t>
+  </si>
+  <si>
+    <t>topologicalOrder</t>
+  </si>
+  <si>
+    <t>Get topological order indices of a DAG.</t>
+  </si>
+  <si>
+    <t>dfs</t>
+  </si>
+  <si>
+    <t>Depth-First Search traversal of a graph</t>
+  </si>
+  <si>
+    <t>top</t>
+  </si>
+  <si>
+    <t>Graph Functions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1471,7 +1483,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1760,43 +1772,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="dotted">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="dotted">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -1824,146 +1799,82 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="dotted">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="dotted">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2287,66 +2198,66 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" t="s">
         <v>446</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>447</v>
-      </c>
-      <c r="C2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D2" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C3" t="s">
         <v>450</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>451</v>
-      </c>
-      <c r="C3" t="s">
-        <v>452</v>
-      </c>
-      <c r="D3" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C4" t="s">
         <v>454</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>455</v>
-      </c>
-      <c r="C4" t="s">
-        <v>456</v>
-      </c>
-      <c r="D4" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C5" t="s">
         <v>458</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>459</v>
-      </c>
-      <c r="C5" t="s">
-        <v>460</v>
-      </c>
-      <c r="D5" t="s">
-        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -2380,10 +2291,10 @@
     </row>
     <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C2" s="15">
         <v>1</v>
@@ -2391,10 +2302,10 @@
     </row>
     <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C3" s="18">
         <v>1</v>
@@ -2402,10 +2313,10 @@
     </row>
     <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C4" s="18">
         <v>1</v>
@@ -2413,10 +2324,10 @@
     </row>
     <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C5" s="18">
         <v>1</v>
@@ -2424,10 +2335,10 @@
     </row>
     <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C6" s="18">
         <v>1</v>
@@ -2435,10 +2346,10 @@
     </row>
     <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C7" s="18">
         <v>2</v>
@@ -2446,10 +2357,10 @@
     </row>
     <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C8" s="18">
         <v>2</v>
@@ -2457,10 +2368,10 @@
     </row>
     <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C9" s="18">
         <v>2</v>
@@ -2468,10 +2379,10 @@
     </row>
     <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C10" s="18">
         <v>2</v>
@@ -2479,10 +2390,10 @@
     </row>
     <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C11" s="18">
         <v>2</v>
@@ -2490,10 +2401,10 @@
     </row>
     <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C12" s="18">
         <v>2</v>
@@ -2501,10 +2412,10 @@
     </row>
     <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C13" s="18">
         <v>2</v>
@@ -2512,10 +2423,10 @@
     </row>
     <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C14" s="18">
         <v>2</v>
@@ -2523,10 +2434,10 @@
     </row>
     <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C15" s="18">
         <v>2</v>
@@ -2534,10 +2445,10 @@
     </row>
     <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C16" s="18">
         <v>3</v>
@@ -2545,10 +2456,10 @@
     </row>
     <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C17" s="18">
         <v>3</v>
@@ -2556,10 +2467,10 @@
     </row>
     <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C18" s="18">
         <v>3</v>
@@ -2567,10 +2478,10 @@
     </row>
     <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C19" s="18">
         <v>3</v>
@@ -2578,10 +2489,10 @@
     </row>
     <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C20" s="18">
         <v>4</v>
@@ -2589,10 +2500,10 @@
     </row>
     <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C21" s="18">
         <v>4</v>
@@ -2600,10 +2511,10 @@
     </row>
     <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C22" s="18">
         <v>4</v>
@@ -2611,10 +2522,10 @@
     </row>
     <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C23" s="18">
         <v>4</v>
@@ -2622,10 +2533,10 @@
     </row>
     <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C24" s="18">
         <v>4</v>
@@ -2633,10 +2544,10 @@
     </row>
     <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C25" s="18">
         <v>5</v>
@@ -2644,10 +2555,10 @@
     </row>
     <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C26" s="18">
         <v>5</v>
@@ -2655,10 +2566,10 @@
     </row>
     <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C27" s="18">
         <v>5</v>
@@ -2666,10 +2577,10 @@
     </row>
     <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C28" s="21">
         <v>5</v>
@@ -2685,7 +2596,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
@@ -2693,367 +2604,400 @@
     <col min="3" max="3" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>327</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" t="s">
         <v>328</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>329</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" t="s">
         <v>330</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>331</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" t="s">
         <v>332</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>333</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" t="s">
         <v>334</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>335</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" t="s">
         <v>336</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" t="s">
         <v>338</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>339</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" t="s">
         <v>340</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>341</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" t="s">
         <v>342</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>343</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" t="s">
         <v>344</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>345</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" t="s">
         <v>346</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B12" t="s">
+        <v>352</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>353</v>
+      </c>
+      <c r="B13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>347</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B14" t="s">
         <v>348</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>461</v>
+      </c>
+      <c r="B15" t="s">
+        <v>462</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>349</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B16" t="s">
         <v>350</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C16">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
-        <v>351</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="C14" s="8">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>355</v>
+      </c>
+      <c r="B17" t="s">
+        <v>356</v>
+      </c>
+      <c r="C17">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>354</v>
-      </c>
-      <c r="C15" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>355</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>356</v>
-      </c>
-      <c r="C16" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>359</v>
+      </c>
+      <c r="B18" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B19" t="s">
+        <v>362</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>371</v>
+      </c>
+      <c r="B20" t="s">
+        <v>372</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>373</v>
+      </c>
+      <c r="B21" t="s">
+        <v>374</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>463</v>
+      </c>
+      <c r="B22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>363</v>
+      </c>
+      <c r="B23" t="s">
+        <v>364</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>365</v>
+      </c>
+      <c r="B24" t="s">
+        <v>366</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>375</v>
+      </c>
+      <c r="B25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>377</v>
+      </c>
+      <c r="B26" t="s">
+        <v>378</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>379</v>
+      </c>
+      <c r="B27" t="s">
+        <v>380</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>381</v>
+      </c>
+      <c r="B28" t="s">
+        <v>382</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>367</v>
+      </c>
+      <c r="B29" t="s">
+        <v>368</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>357</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B30" t="s">
         <v>358</v>
       </c>
-      <c r="C17" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
-        <v>359</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>360</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="C30">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="C19" s="8">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>369</v>
+      </c>
+      <c r="B31" t="s">
+        <v>370</v>
+      </c>
+      <c r="C31">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="C20" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="C21" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="C22" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
-        <v>369</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>370</v>
-      </c>
-      <c r="C23" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
-        <v>371</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>372</v>
-      </c>
-      <c r="C24" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
-        <v>373</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>374</v>
-      </c>
-      <c r="C25" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B26" s="29" t="s">
-        <v>376</v>
-      </c>
-      <c r="C26" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
-        <v>377</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="C27" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="B28" s="29" t="s">
-        <v>380</v>
-      </c>
-      <c r="C28" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
-        <v>381</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>382</v>
-      </c>
-      <c r="C29" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>467</v>
+      </c>
+      <c r="B32" t="s">
+        <v>468</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>465</v>
+      </c>
+      <c r="B33" t="s">
+        <v>466</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>383</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B34" t="s">
         <v>384</v>
       </c>
-      <c r="C30" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
+      <c r="C34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>385</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B35" t="s">
         <v>386</v>
       </c>
-      <c r="C31" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="24" t="s">
+      <c r="C35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>387</v>
       </c>
-      <c r="B32" s="29" t="s">
-        <v>388</v>
-      </c>
-      <c r="C32" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
-        <v>389</v>
-      </c>
-      <c r="B33" s="31" t="s">
-        <v>462</v>
-      </c>
-      <c r="C33" s="12">
-        <v>4</v>
+      <c r="B36" t="s">
+        <v>460</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4671,7 +4615,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -4725,12 +4669,23 @@
     </row>
     <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>469</v>
+      </c>
+      <c r="B5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C5" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>49</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C6" s="3">
         <v>4</v>
       </c>
     </row>
